--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486728_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486728_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3396</v>
+        <v>6.0279</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0303</v>
+        <v>4.3958</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3093</v>
+        <v>1.6321</v>
       </c>
       <c r="G2" t="n">
         <v>5.1025</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9986</v>
+        <v>-0.3103</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8554</v>
+        <v>-0.4899</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1432</v>
+        <v>0.1796</v>
       </c>
       <c r="V2" t="n">
         <v>0.6565</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9065</v>
+        <v>3.8942</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0797</v>
+        <v>0.5144</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8268</v>
+        <v>3.3798</v>
       </c>
       <c r="G3" t="n">
         <v>2.1135</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9088</v>
+        <v>0.8965</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6339</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2749</v>
+        <v>0.8279</v>
       </c>
       <c r="V3" t="n">
         <v>1.2703</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8082</v>
+        <v>3.6165</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5405</v>
+        <v>3.92</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2676</v>
+        <v>-0.3035</v>
       </c>
       <c r="G4" t="n">
         <v>1.1326</v>
@@ -766,13 +766,13 @@
         <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0191</v>
+        <v>0.8275</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8544</v>
+        <v>0.2339</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1647</v>
+        <v>0.5936</v>
       </c>
       <c r="V4" t="n">
         <v>1.2703</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.289</v>
+        <v>2.3553</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8941</v>
+        <v>3.6872</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6051</v>
+        <v>-1.3319</v>
       </c>
       <c r="G5" t="n">
         <v>1.4219</v>
@@ -844,13 +844,13 @@
         <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.717</v>
       </c>
       <c r="T5" t="n">
-        <v>0.772</v>
+        <v>0.5651</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1212</v>
+        <v>0.1519</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9421</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0428</v>
+        <v>0.8883</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3767</v>
+        <v>0.1956</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4195</v>
+        <v>0.6926</v>
       </c>
       <c r="G6" t="n">
         <v>1.3638</v>
@@ -922,13 +922,13 @@
         <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1971</v>
+        <v>-0.3517</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0209</v>
+        <v>-0.4486</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1762</v>
+        <v>0.097</v>
       </c>
       <c r="V6" t="n">
         <v>1.2277</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6051</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9462</v>
+        <v>1.0496</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5513</v>
+        <v>-1.7003</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8682</v>
@@ -1000,13 +1000,13 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4248</v>
+        <v>0.3793</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1383</v>
+        <v>-0.0348</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5631</v>
+        <v>0.4141</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5133</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8717</v>
+        <v>-1.7131</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7602</v>
+        <v>-2.6016</v>
       </c>
       <c r="F8" t="n">
         <v>0.8885</v>
@@ -1078,10 +1078,10 @@
         <v>2.3169</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3862</v>
+        <v>0.5448</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2763</v>
+        <v>-0.1177</v>
       </c>
       <c r="U8" t="n">
         <v>0.6624</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.8909</v>
+        <v>-5.124</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8025</v>
+        <v>-4.3336</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0884</v>
+        <v>-0.7904</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3348</v>
@@ -1156,13 +1156,13 @@
         <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1157</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3866</v>
+        <v>0.0822</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5023</v>
+        <v>0.8003</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5133</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.0184</v>
+        <v>9.294400000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>6.551399999999999</v>
+        <v>6.827400000000001</v>
       </c>
       <c r="F10" t="n">
         <v>2.4669</v>
@@ -1234,10 +1234,10 @@
         <v>13.5153</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3096</v>
+        <v>3.5857</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4172</v>
+        <v>-0.1412</v>
       </c>
       <c r="U10" t="n">
         <v>3.7268</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.7718</v>
+        <v>2.2269</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3898</v>
+        <v>3.0796</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6181</v>
+        <v>-0.8527</v>
       </c>
       <c r="G11" t="n">
         <v>3.7051</v>
@@ -1312,13 +1312,13 @@
         <v>2.3169</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.0897</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.3109</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6352</v>
+        <v>0.4006</v>
       </c>
       <c r="V11" t="n">
         <v>0.9421</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2737</v>
+        <v>2.1355</v>
       </c>
       <c r="E12" t="n">
-        <v>2.754</v>
+        <v>3.478</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4804</v>
+        <v>-1.3425</v>
       </c>
       <c r="G12" t="n">
         <v>0.2637</v>
@@ -1390,13 +1390,13 @@
         <v>2.51</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4341</v>
+        <v>-0.5723</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4899</v>
+        <v>-0.766</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0558</v>
+        <v>0.1937</v>
       </c>
       <c r="V12" t="n">
         <v>0.8995</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2834</v>
+        <v>0.1592</v>
       </c>
       <c r="E13" t="n">
         <v>0.5389</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2555</v>
+        <v>-0.3797</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1126</v>
@@ -1468,13 +1468,13 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6619</v>
+        <v>-0.786</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4415</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2204</v>
+        <v>-0.3446</v>
       </c>
       <c r="V13" t="n">
         <v>0.2856</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1196</v>
+        <v>0.0265</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1178</v>
+        <v>-0.911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9983</v>
+        <v>0.9375</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6217</v>
@@ -1546,13 +1546,13 @@
         <v>0.5792</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0771</v>
+        <v>0.0689</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5518</v>
+        <v>-0.345</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4747</v>
+        <v>0.4139</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.226</v>
+        <v>-0.5526</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3681</v>
+        <v>-2.6072</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5941</v>
+        <v>2.0547</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1566</v>
+        <v>-0.2629</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9169</v>
+        <v>-0.5794</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2397</v>
+        <v>0.3165</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0176</v>
+        <v>-1.2969</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7094</v>
+        <v>-0.6481</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6918</v>
+        <v>-0.6488</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.139</v>
+        <v>1.034</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2075</v>
+        <v>0.0687</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9314</v>
+        <v>0.9653</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>0.386</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3857</v>
+        <v>-0.345</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0003</v>
+        <v>0.2484</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.096</v>
+        <v>-0.6879</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8141</v>
+        <v>-0.3559</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7181</v>
+        <v>-0.332</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2629</v>
+        <v>-1.1566</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5794</v>
+        <v>-0.9169</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3165</v>
+        <v>-0.2397</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2969</v>
+        <v>-0.0176</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6481</v>
+        <v>-0.7094</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6488</v>
+        <v>0.6918</v>
       </c>
       <c r="M16" t="n">
-        <v>1.034</v>
+        <v>-1.139</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0687</v>
+        <v>-0.2075</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9653</v>
+        <v>-0.9314</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.64</v>
+        <v>-0.0759</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5518</v>
+        <v>-0.3383</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0882</v>
+        <v>0.2624</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4452</v>
+        <v>-1.6002</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8802</v>
+        <v>-1.0206</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5796</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3774</v>
+        <v>-0.4138</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4761</v>
+        <v>-0.9654</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9013</v>
+        <v>0.5516</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3005</v>
+        <v>-0.6895</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5446</v>
+        <v>-0.6895</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2442</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0769</v>
+        <v>0.2756</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.2759</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1454</v>
+        <v>0.5516</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3862</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3183</v>
+        <v>-0.3448</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3511</v>
+        <v>-0.3311</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0328</v>
+        <v>-0.0137</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6747</v>
+        <v>-1.6241</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0206</v>
+        <v>0.3318</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6541</v>
+        <v>-1.9559</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4138</v>
+        <v>-3.3275</v>
       </c>
       <c r="H18" t="n">
+        <v>-0.5446</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-2.7829</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.9124</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.2682</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.6442</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-2.4151</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.2764</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.1387</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.7723</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.5516</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.6895</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.6895</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2756</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.2759</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.5516</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.3862</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4193</v>
+        <v>-0.2965</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3311</v>
+        <v>-0.5314</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0882</v>
+        <v>0.2348</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>D. MARTINEZ DE LA SERNA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3646</v>
+        <v>-2.513</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1853</v>
+        <v>-2.2232</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1794</v>
+        <v>-0.2898</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3275</v>
+        <v>-0.1381</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5446</v>
+        <v>0.6757</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7829</v>
+        <v>-0.8138</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9124</v>
+        <v>0.3311</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2682</v>
+        <v>0.3311</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6442</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4151</v>
+        <v>-0.4692</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2764</v>
+        <v>0.3447</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1387</v>
+        <v>-0.8138</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7723</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0371</v>
+        <v>-0.2896</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0485</v>
+        <v>-0.2759</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0113</v>
+        <v>-0.0137</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2277</v>
+        <v>-1.3129</v>
       </c>
       <c r="W19" t="n">
-        <v>2.741</v>
+        <v>-1.3129</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MARTINEZ DE LA SERNA</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5875</v>
+        <v>-2.6325</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2232</v>
+        <v>-2.0178</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3643</v>
+        <v>-0.6147</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1381</v>
+        <v>-2.3774</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6757</v>
+        <v>-0.4761</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8138</v>
+        <v>-1.9013</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3311</v>
+        <v>-0.3005</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3311</v>
+        <v>-0.5446</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.2442</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4692</v>
+        <v>-2.0769</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3447</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8138</v>
+        <v>-2.1454</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3641</v>
+        <v>0.131</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2759</v>
+        <v>0.2134</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0882</v>
+        <v>-0.0824</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3129</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.3129</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8336</v>
+        <v>-3.2669</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2766</v>
+        <v>-0.7595</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5571</v>
+        <v>-2.5074</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5251</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0149</v>
+        <v>-0.4481</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7725</v>
+        <v>-0.2554</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2423</v>
+        <v>-0.1927</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9421</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.0183</v>
+        <v>-8.3291</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.466999999999999</v>
+        <v>-2.466899999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.551600000000001</v>
+        <v>-5.8621</v>
       </c>
       <c r="G22" t="n">
         <v>-4.966900000000001</v>
@@ -2140,7 +2140,7 @@
         <v>1.724799999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.6918</v>
+        <v>-6.691800000000001</v>
       </c>
       <c r="J22" t="n">
         <v>10.0778</v>
@@ -2149,13 +2149,13 @@
         <v>1.3853</v>
       </c>
       <c r="L22" t="n">
-        <v>8.692600000000002</v>
+        <v>8.692600000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-15.0449</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3399</v>
+        <v>0.3398999999999999</v>
       </c>
       <c r="O22" t="n">
         <v>-15.3844</v>
@@ -2170,13 +2170,13 @@
         <v>13.5154</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.3096</v>
+        <v>-2.620200000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.7268</v>
+        <v>-3.7271</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4172</v>
+        <v>1.1067</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7415999999999997</v>
